--- a/FPE/Input/input_famd_cali_29102025.xlsx
+++ b/FPE/Input/input_famd_cali_29102025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/FPE/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F677BCC78F79A8D366075C52F37BD272BA478D84" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{078AA4AD-DA30-43BC-890B-1A51DAEB5D25}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F677BCC78F79A8D366075C52F37BD272BA478D84" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A754486F-D5EE-4C3A-8215-23642CD1AADF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -725,6 +725,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="18" max="18" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
